--- a/FLORES DE ESTRADA/Agosto/PRORRATEO Agosto Estrada.xlsx
+++ b/FLORES DE ESTRADA/Agosto/PRORRATEO Agosto Estrada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D901ADA1-E72D-4E0A-97B7-24B7F7AF6222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B4CB4E-6D94-4152-90DD-148E534925E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -274,10 +274,7 @@
     <t>Federico</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/08  LIQUIDACION : JULIO</t>
-  </si>
-  <si>
-    <t>LE PUSIMOS NO PAGA LAS EXTRAORDINARIAS (DE $27230) CUANDO SI LAS HABIA PAGADO</t>
+    <t>EXPENSAS - VENCIMIENTO 15/09  LIQUIDACION : AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -413,7 +410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,12 +426,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -621,7 +612,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -732,6 +723,10 @@
     <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -753,11 +748,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1107,7 +1097,7 @@
     <col min="5" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="6" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" style="6" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" customWidth="1"/>
     <col min="11" max="11" width="12.140625" customWidth="1"/>
@@ -1117,22 +1107,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1165,13 +1155,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="65">
+      <c r="J4" s="67">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="66"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1348,23 +1338,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>663787.08654741221</v>
+        <v>800086.0071855844</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>663787.08654741221</v>
+        <v>800086.0071855844</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>58413.263616172284</v>
+        <v>70407.568632331429</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>722200.35016358446</v>
+        <v>870493.57581791584</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1376,7 +1366,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>800086.0071855844</v>
+        <v>948379.2328399159</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1485,10 +1475,10 @@
       <c r="A15" s="11">
         <v>5</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="65" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="55" t="s">
@@ -1498,26 +1488,26 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>77885.657021999999</v>
+        <v>107511.897022</v>
       </c>
       <c r="G15" s="62">
-        <f>F15-27230</f>
-        <v>50655.657021999999</v>
+        <f>F15</f>
+        <v>107511.897022</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
-        <v>27230</v>
+        <v>0</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>2396.2400000000002</v>
+        <v>0</v>
       </c>
       <c r="K15" s="44">
         <f>H15+J15+I15</f>
-        <v>29626.240000000002</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
@@ -1529,11 +1519,9 @@
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>107511.897022</v>
-      </c>
-      <c r="P15" s="71" t="s">
-        <v>83</v>
-      </c>
+        <v>77885.657021999999</v>
+      </c>
+      <c r="P15" s="59"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
@@ -1552,26 +1540,25 @@
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>229160.65879505922</v>
+        <v>80088.079200000007</v>
       </c>
       <c r="G16" s="62">
-        <f>F16</f>
-        <v>229160.65879505922</v>
+        <v>52088</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28000.079200000007</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2464.006969600001</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>0</v>
+        <v>30464.086169600007</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1583,7 +1570,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>80088.079200000007</v>
+        <v>110552.1653696</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1706,7 +1693,7 @@
         <v>80088.079200000007</v>
       </c>
       <c r="G19" s="62">
-        <f>F19</f>
+        <f t="shared" si="4"/>
         <v>80088.079200000007</v>
       </c>
       <c r="H19" s="8">
@@ -1752,25 +1739,26 @@
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>-4377.2293319999881</v>
+        <v>248716.34515478404</v>
       </c>
       <c r="G20" s="62">
-        <v>0</v>
+        <f>F20</f>
+        <v>248716.34515478404</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
-        <v>-4377.2293319999881</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>-385.19618121599899</v>
+        <v>0</v>
       </c>
       <c r="K20" s="44">
         <f>H20+J20+I20</f>
-        <v>-4762.4255132159869</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
@@ -1782,7 +1770,7 @@
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>248716.34515478404</v>
+        <v>253478.77066800001</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1851,23 +1839,23 @@
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>150365.36869799998</v>
+        <v>313962.88984142395</v>
       </c>
       <c r="G22" s="62"/>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>150365.36869799998</v>
+        <v>313962.88984142395</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>13232.152445423999</v>
+        <v>27628.734306045309</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>163597.52114342398</v>
+        <v>341591.62414746924</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
@@ -1879,7 +1867,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>313962.88984142395</v>
+        <v>491956.99284546921</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1897,23 +1885,23 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>308691.5767484465</v>
+        <v>424954.42361230979</v>
       </c>
       <c r="G23" s="62"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>308691.5767484465</v>
+        <v>424954.42361230979</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>27164.858753863296</v>
+        <v>37395.989277883265</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>335856.43550230982</v>
+        <v>462350.41289019305</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1925,7 +1913,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>424954.42361230979</v>
+        <v>551448.40100019309</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1994,25 +1982,25 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>369989.25462959788</v>
+        <v>428598.78514700249</v>
       </c>
       <c r="G25" s="62">
         <v>57949</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>312040.25462959788</v>
+        <v>370649.78514700249</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>27459.542407404617</v>
+        <v>32617.181092936222</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>339499.79703700251</v>
+        <v>403266.96623993869</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2024,7 +2012,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>428598.78514700249</v>
+        <v>492365.95434993866</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2044,23 +2032,25 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>960634.16311672679</v>
-      </c>
-      <c r="G26" s="62"/>
+        <v>1229173.3314329986</v>
+      </c>
+      <c r="G26" s="62">
+        <v>159147</v>
+      </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>960634.16311672679</v>
+        <v>1070026.3314329986</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>84535.806354271961</v>
+        <v>94162.317166103894</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1045169.9694709987</v>
+        <v>1164188.6485991026</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2072,7 +2062,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1229173.3314329986</v>
+        <v>1348192.0105611025</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2141,23 +2131,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>5949.2986157917376</v>
+        <v>8552.0114300134101</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>73554.964704334197</v>
+        <v>105733.95949834761</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2169,7 +2159,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2187,23 +2177,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
       <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>5949.2986157917376</v>
+        <v>8552.0114300134101</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>73554.964704334197</v>
+        <v>105733.95949834761</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2215,7 +2205,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>97181.948068334197</v>
+        <v>129360.94286234761</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2233,11 +2223,11 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>97666.237953030359</v>
+        <v>23626.983364</v>
       </c>
       <c r="G30" s="62">
         <f>F30</f>
-        <v>97666.237953030359</v>
+        <v>23626.983364</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
@@ -2432,23 +2422,23 @@
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>23626.983364</v>
+        <v>49333.141264031998</v>
       </c>
       <c r="G34" s="62"/>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>23626.983364</v>
+        <v>49333.141264031998</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>2079.1745360320001</v>
+        <v>4341.3164312348163</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>25706.157900031998</v>
+        <v>53674.457695266814</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
@@ -2460,15 +2450,15 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>49333.141264031998</v>
+        <v>77301.441059266814</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2476,15 +2466,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>3918241.045273358</v>
+        <v>4806015.734914802</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1341031.5093240894</v>
+        <v>1554639.1810947841</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>2577209.5359492684</v>
+        <v>3251376.5538200201</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2492,7 +2482,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>226794.43916353563</v>
+        <v>286121.13673616177</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2505,7 +2495,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>4806015.734914802</v>
+        <v>5539509.4503581822</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3281,11 +3271,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>
